--- a/education_forms/043_enrollment_package_agreement--education_forms.xlsx
+++ b/education_forms/043_enrollment_package_agreement--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>student_status</t>
+          <t>student_status_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Student Status</t>
+          <t>Student Status 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>student_signature</t>
+          <t>student_signature_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Student Signature</t>
+          <t>Student Signature 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>student_signature</t>
+          <t>student_signature_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Student Signature</t>
+          <t>Student Signature 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1160,51 +1160,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'credit_card'}</t>
+          <t>credit card</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'bank_transfer'}</t>
+          <t>bank transfer</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'signature'}</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'signature'}</t>
+          <t>signature</t>
         </is>
       </c>
     </row>
@@ -1233,46 +1233,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>student_signature_choices</t>
+          <t>student_signature_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'signature'}</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'signature'}</t>
+          <t>signature</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>student_signature_choices</t>
+          <t>student_signature_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
